--- a/insights/20251230-20241230-insights/comparison_insights.xlsx
+++ b/insights/20251230-20241230-insights/comparison_insights.xlsx
@@ -710,13 +710,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="C4">
         <v>1705</v>
       </c>
       <c r="D4">
-        <v>0.7038123167155426</v>
+        <v>0.5865102639296188</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>24126.56</v>
+        <v>927.9400000000001</v>
       </c>
       <c r="I2">
         <v>897.27</v>
@@ -825,16 +825,16 @@
         <v>911.72</v>
       </c>
       <c r="K2">
-        <v>2588.885173916436</v>
+        <v>3.418146154446273</v>
       </c>
       <c r="L2">
-        <v>2546.268591234151</v>
+        <v>1.779054973018035</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>3.778905902872187</v>
+        <v>98.25204215789813</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7973.466361111111</v>
+        <v>3641.27636111111</v>
       </c>
       <c r="I3">
         <v>6241.3</v>
@@ -875,16 +875,16 @@
         <v>5715.51</v>
       </c>
       <c r="K3">
-        <v>27.75329436353181</v>
+        <v>-41.65836666862496</v>
       </c>
       <c r="L3">
-        <v>39.50577220774893</v>
+        <v>-36.29131326668818</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>71.68162178342141</v>
+        <v>156.9644661152814</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>6632.707944444444</v>
+        <v>999.1479444444444</v>
       </c>
       <c r="I4">
         <v>1145.59</v>
@@ -925,16 +925,16 @@
         <v>1191.77</v>
       </c>
       <c r="K4">
-        <v>478.97746527505</v>
+        <v>-12.78311224395774</v>
       </c>
       <c r="L4">
-        <v>456.5426168173761</v>
+        <v>-16.16268705837163</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>17.96807593493132</v>
+        <v>119.2786320210726</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6517.657180555555</v>
+        <v>2134.097180555556</v>
       </c>
       <c r="I5">
         <v>1521.8</v>
@@ -975,16 +975,16 @@
         <v>2522.72</v>
       </c>
       <c r="K5">
-        <v>328.2860547086053</v>
+        <v>40.23506246258089</v>
       </c>
       <c r="L5">
-        <v>158.3583267487298</v>
+        <v>-15.40491292907829</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>38.70593267050243</v>
+        <v>118.2101744468486</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>5918.792027777778</v>
+        <v>644.8220277777777</v>
       </c>
       <c r="I7">
         <v>916.76</v>
@@ -1075,16 +1075,16 @@
         <v>1436.29</v>
       </c>
       <c r="K7">
-        <v>545.6206671078339</v>
+        <v>-29.6629403794038</v>
       </c>
       <c r="L7">
-        <v>312.0889254800757</v>
+        <v>-55.10502560222672</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>24.26660699107648</v>
+        <v>222.7420804698351</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>12629.65273611111</v>
+        <v>3965.262736111112</v>
       </c>
       <c r="I9">
         <v>3172.27</v>
@@ -1175,16 +1175,16 @@
         <v>3197.82</v>
       </c>
       <c r="K9">
-        <v>298.1266643794857</v>
+        <v>24.99764320537381</v>
       </c>
       <c r="L9">
-        <v>294.9457047648432</v>
+        <v>23.9989347777896</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>25.31993608071812</v>
+        <v>80.64585407866888</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>9.845520063740397</v>
       </c>
       <c r="H10">
-        <v>15596.48590277778</v>
+        <v>2685.515902777778</v>
       </c>
       <c r="I10">
         <v>2531.45</v>
@@ -1225,19 +1225,19 @@
         <v>2761.07</v>
       </c>
       <c r="K10">
-        <v>516.1087875635616</v>
+        <v>6.086073308885338</v>
       </c>
       <c r="L10">
-        <v>464.8710790663685</v>
+        <v>-2.736406437439923</v>
       </c>
       <c r="M10">
-        <v>1555.763019391338</v>
+        <v>9035.297826723703</v>
       </c>
       <c r="N10">
-        <v>17.70315452603491</v>
+        <v>102.8133922850381</v>
       </c>
       <c r="O10">
-        <v>-81.34755003164345</v>
+        <v>8.32655009893392</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>11.13954799809135</v>
       </c>
       <c r="H11">
-        <v>13692.78368055555</v>
+        <v>1055.803680555556</v>
       </c>
       <c r="I11">
         <v>6043.89</v>
@@ -1275,19 +1275,19 @@
         <v>6723.41</v>
       </c>
       <c r="K11">
-        <v>126.5558056244497</v>
+        <v>-82.53105730654337</v>
       </c>
       <c r="L11">
-        <v>103.6583174394475</v>
+        <v>-84.29660424463842</v>
       </c>
       <c r="M11">
-        <v>187.1131582717042</v>
+        <v>2426.682201611424</v>
       </c>
       <c r="N11">
-        <v>49.1018492430256</v>
+        <v>636.8049405228627</v>
       </c>
       <c r="O11">
-        <v>-62.83984286260033</v>
+        <v>381.9323919671563</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>-3.693789290551787</v>
       </c>
       <c r="H15">
-        <v>5371.428125</v>
+        <v>919.3681250000002</v>
       </c>
       <c r="I15">
         <v>324.42</v>
@@ -1475,19 +1475,19 @@
         <v>615.13</v>
       </c>
       <c r="K15">
-        <v>1555.701906479255</v>
+        <v>183.3882390111584</v>
       </c>
       <c r="L15">
-        <v>773.2183644107749</v>
+        <v>49.45915903955265</v>
       </c>
       <c r="M15">
-        <v>323.9067822395929</v>
+        <v>1892.432370330437</v>
       </c>
       <c r="N15">
-        <v>11.45188924965835</v>
+        <v>66.90791025629694</v>
       </c>
       <c r="O15">
-        <v>-90.8728855009994</v>
+        <v>-46.67463643029054</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>24678.82263888889</v>
+        <v>1171.972638888889</v>
       </c>
       <c r="I17">
         <v>928.53</v>
@@ -1575,16 +1575,16 @@
         <v>913.71</v>
       </c>
       <c r="K17">
-        <v>2557.83794157312</v>
+        <v>26.21806930189535</v>
       </c>
       <c r="L17">
-        <v>2600.946978679109</v>
+        <v>28.26527441845759</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17">
-        <v>3.702405148615865</v>
+        <v>77.96342420299678</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1625,19 +1625,19 @@
         <v>1131.43</v>
       </c>
       <c r="K18">
-        <v>62.33872780488836</v>
+        <v>62.33872780488832</v>
       </c>
       <c r="L18">
-        <v>51.42269198173012</v>
+        <v>51.42269198173008</v>
       </c>
       <c r="M18">
-        <v>720.8842476478982</v>
+        <v>720.8842476478984</v>
       </c>
       <c r="N18">
-        <v>66.04029996512378</v>
+        <v>66.04029996512379</v>
       </c>
       <c r="O18">
-        <v>-32.97607770669334</v>
+        <v>-32.97607770669331</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>20.37130406597761</v>
       </c>
       <c r="H19">
-        <v>3508.192694444446</v>
+        <v>3508.192694444445</v>
       </c>
       <c r="I19">
         <v>2522.18</v>
@@ -1675,19 +1675,19 @@
         <v>2597.04</v>
       </c>
       <c r="K19">
-        <v>39.09366874863991</v>
+        <v>39.09366874863989</v>
       </c>
       <c r="L19">
-        <v>35.08427650111072</v>
+        <v>35.0842765011107</v>
       </c>
       <c r="M19">
-        <v>800.2907036566316</v>
+        <v>800.2907036566319</v>
       </c>
       <c r="N19">
         <v>74.02786067346466</v>
       </c>
       <c r="O19">
-        <v>-27.25390361191301</v>
+        <v>-27.25390361191299</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>-100</v>
       </c>
       <c r="H22">
-        <v>4790.374222222222</v>
+        <v>406.8142222222223</v>
       </c>
       <c r="I22">
         <v>568.51</v>
@@ -1825,16 +1825,16 @@
         <v>644.84</v>
       </c>
       <c r="K22">
-        <v>742.6191662806673</v>
+        <v>-28.44202877306956</v>
       </c>
       <c r="L22">
-        <v>642.8779576673627</v>
+        <v>-36.91237791975959</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>13.46116128064966</v>
+        <v>158.5096992129632</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>6500</v>
+        <v>250</v>
       </c>
       <c r="I24">
         <v>208.58</v>
@@ -1925,16 +1925,16 @@
         <v>250.06</v>
       </c>
       <c r="K24">
-        <v>3016.310288618276</v>
+        <v>19.85808802377984</v>
       </c>
       <c r="L24">
-        <v>2499.376149724066</v>
+        <v>-0.02399424138206921</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>3.847076923076923</v>
+        <v>100.024</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -2016,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>5205.323333333334</v>
+        <v>753.2633333333334</v>
       </c>
       <c r="I26">
         <v>884.78</v>
@@ -2025,16 +2025,16 @@
         <v>615.88</v>
       </c>
       <c r="K26">
-        <v>488.3183766962786</v>
+        <v>-14.86433539034184</v>
       </c>
       <c r="L26">
-        <v>745.1846680089195</v>
+        <v>22.30683466476155</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26">
-        <v>11.83173379559515</v>
+        <v>81.761579615805</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>6323.932652777778</v>
+        <v>1032.832652777778</v>
       </c>
       <c r="I28">
         <v>868.23</v>
@@ -2125,16 +2125,16 @@
         <v>589.33</v>
       </c>
       <c r="K28">
-        <v>628.3706682305124</v>
+        <v>18.95841571677754</v>
       </c>
       <c r="L28">
-        <v>973.0715647901477</v>
+        <v>75.25540067157239</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28">
-        <v>9.319042949344784</v>
+        <v>57.05958253885678</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2225,16 +2225,16 @@
         <v>581.37</v>
       </c>
       <c r="K30">
-        <v>60.37135188557173</v>
+        <v>60.37135188557176</v>
       </c>
       <c r="L30">
-        <v>110.576188810721</v>
+        <v>110.5761888107211</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>47.48875006465532</v>
+        <v>47.48875006465531</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>8296.319166666666</v>
+        <v>522.3491666666666</v>
       </c>
       <c r="I31">
         <v>613.28</v>
@@ -2275,16 +2275,16 @@
         <v>587.05</v>
       </c>
       <c r="K31">
-        <v>1252.778366597095</v>
+        <v>-14.82696864944778</v>
       </c>
       <c r="L31">
-        <v>1313.221900462766</v>
+        <v>-11.02134968628453</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31">
-        <v>7.076029600677328</v>
+        <v>112.3865103004217</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>15616.36240277778</v>
+        <v>1061.552402777778</v>
       </c>
       <c r="I33">
         <v>781.34</v>
@@ -2375,16 +2375,16 @@
         <v>980.3099999999999</v>
       </c>
       <c r="K33">
-        <v>1898.664141446461</v>
+        <v>35.86305613148921</v>
       </c>
       <c r="L33">
-        <v>1493.002458689371</v>
+        <v>8.287419569093236</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
       <c r="N33">
-        <v>6.277454215750182</v>
+        <v>92.34683068257489</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>21369.86</v>
+        <v>821.92</v>
       </c>
       <c r="I34">
         <v>824.1799999999999</v>
@@ -2425,16 +2425,16 @@
         <v>846.78</v>
       </c>
       <c r="K34">
-        <v>2492.863209493072</v>
+        <v>-0.274211943992816</v>
       </c>
       <c r="L34">
-        <v>2423.661399655165</v>
+        <v>-2.935827487659134</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
       <c r="N34">
-        <v>3.962496712659792</v>
+        <v>103.024625267666</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>5107.374888888889</v>
+        <v>518.3348888888888</v>
       </c>
       <c r="I35">
         <v>870.85</v>
@@ -2475,16 +2475,16 @@
         <v>410.8</v>
       </c>
       <c r="K35">
-        <v>486.4815856793809</v>
+        <v>-40.47942942080854</v>
       </c>
       <c r="L35">
-        <v>1143.275289408201</v>
+        <v>26.17694471491938</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>8.043270935401605</v>
+        <v>79.25378144631507</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>5627.4</v>
+        <v>216.44</v>
       </c>
       <c r="I36">
         <v>208.58</v>
@@ -2525,16 +2525,16 @@
         <v>144.38</v>
       </c>
       <c r="K36">
-        <v>2597.957618180075</v>
+        <v>3.768338287467631</v>
       </c>
       <c r="L36">
-        <v>3797.631250865771</v>
+        <v>49.90995982823106</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36">
-        <v>2.565660873582827</v>
+        <v>66.70670855664386</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>16223.29</v>
+        <v>623.97</v>
       </c>
       <c r="I37">
         <v>495.43</v>
@@ -2575,16 +2575,16 @@
         <v>624.21</v>
       </c>
       <c r="K37">
-        <v>3174.587731869285</v>
+        <v>25.94513856649779</v>
       </c>
       <c r="L37">
-        <v>2499.011550599958</v>
+        <v>-0.03844859902917433</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37">
-        <v>3.847616605509733</v>
+        <v>100.0384633876629</v>
       </c>
       <c r="O37">
         <v>0</v>
